--- a/verification_detailed.xlsx
+++ b/verification_detailed.xlsx
@@ -27195,13 +27195,13 @@
         <v>185</v>
       </c>
       <c r="E955" t="n">
-        <v>10665</v>
+        <v>10776</v>
       </c>
       <c r="F955" t="n">
-        <v>4204</v>
+        <v>4314</v>
       </c>
       <c r="G955" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
     </row>
     <row r="956">
@@ -27369,13 +27369,13 @@
         <v>191</v>
       </c>
       <c r="E961" t="n">
-        <v>13237</v>
+        <v>13348</v>
       </c>
       <c r="F961" t="n">
-        <v>4068</v>
+        <v>4178</v>
       </c>
       <c r="G961" t="n">
-        <v>9169</v>
+        <v>9170</v>
       </c>
     </row>
     <row r="962">
@@ -27657,13 +27657,13 @@
       </c>
       <c r="D971" s="3" t="inlineStr"/>
       <c r="E971" s="3" t="n">
-        <v>1673326</v>
+        <v>1673548</v>
       </c>
       <c r="F971" s="3" t="n">
-        <v>617562</v>
+        <v>617782</v>
       </c>
       <c r="G971" s="3" t="n">
-        <v>1055764</v>
+        <v>1055766</v>
       </c>
     </row>
     <row r="972">
@@ -27947,13 +27947,13 @@
         <v>9</v>
       </c>
       <c r="E982" t="n">
-        <v>9754</v>
+        <v>9643</v>
       </c>
       <c r="F982" t="n">
-        <v>2701</v>
+        <v>2591</v>
       </c>
       <c r="G982" t="n">
-        <v>7053</v>
+        <v>7052</v>
       </c>
     </row>
     <row r="983">
@@ -28643,13 +28643,13 @@
         <v>33</v>
       </c>
       <c r="E1006" t="n">
-        <v>3456</v>
+        <v>3345</v>
       </c>
       <c r="F1006" t="n">
-        <v>1909</v>
+        <v>1799</v>
       </c>
       <c r="G1006" t="n">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="1007">
@@ -32817,13 +32817,13 @@
       </c>
       <c r="D1150" s="3" t="inlineStr"/>
       <c r="E1150" s="3" t="n">
-        <v>1706449</v>
+        <v>1706227</v>
       </c>
       <c r="F1150" s="3" t="n">
-        <v>646204</v>
+        <v>645984</v>
       </c>
       <c r="G1150" s="3" t="n">
-        <v>1060245</v>
+        <v>1060243</v>
       </c>
     </row>
     <row r="1151">

--- a/verification_detailed.xlsx
+++ b/verification_detailed.xlsx
@@ -25368,13 +25368,13 @@
         <v>122</v>
       </c>
       <c r="E892" t="n">
-        <v>6083</v>
+        <v>6194</v>
       </c>
       <c r="F892" t="n">
-        <v>2240</v>
+        <v>2350</v>
       </c>
       <c r="G892" t="n">
-        <v>3843</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="893">
@@ -25426,13 +25426,13 @@
         <v>124</v>
       </c>
       <c r="E894" t="n">
-        <v>6071</v>
+        <v>6182</v>
       </c>
       <c r="F894" t="n">
-        <v>2339</v>
+        <v>2449</v>
       </c>
       <c r="G894" t="n">
-        <v>3732</v>
+        <v>3733</v>
       </c>
     </row>
     <row r="895">
@@ -25455,13 +25455,13 @@
         <v>125</v>
       </c>
       <c r="E895" t="n">
-        <v>7337</v>
+        <v>7448</v>
       </c>
       <c r="F895" t="n">
-        <v>2402</v>
+        <v>2512</v>
       </c>
       <c r="G895" t="n">
-        <v>4935</v>
+        <v>4936</v>
       </c>
     </row>
     <row r="896">
@@ -26064,13 +26064,13 @@
         <v>146</v>
       </c>
       <c r="E916" t="n">
-        <v>7995</v>
+        <v>8106</v>
       </c>
       <c r="F916" t="n">
-        <v>3391</v>
+        <v>3501</v>
       </c>
       <c r="G916" t="n">
-        <v>4604</v>
+        <v>4605</v>
       </c>
     </row>
     <row r="917">
@@ -27657,13 +27657,13 @@
       </c>
       <c r="D971" s="3" t="inlineStr"/>
       <c r="E971" s="3" t="n">
-        <v>1673548</v>
+        <v>1673992</v>
       </c>
       <c r="F971" s="3" t="n">
-        <v>617782</v>
+        <v>618222</v>
       </c>
       <c r="G971" s="3" t="n">
-        <v>1055766</v>
+        <v>1055770</v>
       </c>
     </row>
     <row r="972">
@@ -28005,13 +28005,13 @@
         <v>11</v>
       </c>
       <c r="E984" t="n">
-        <v>27891</v>
+        <v>27780</v>
       </c>
       <c r="F984" t="n">
-        <v>11571</v>
+        <v>11461</v>
       </c>
       <c r="G984" t="n">
-        <v>16320</v>
+        <v>16319</v>
       </c>
     </row>
     <row r="985">
@@ -32817,13 +32817,13 @@
       </c>
       <c r="D1150" s="3" t="inlineStr"/>
       <c r="E1150" s="3" t="n">
-        <v>1706227</v>
+        <v>1706116</v>
       </c>
       <c r="F1150" s="3" t="n">
-        <v>645984</v>
+        <v>645874</v>
       </c>
       <c r="G1150" s="3" t="n">
-        <v>1060243</v>
+        <v>1060242</v>
       </c>
     </row>
     <row r="1151">
